--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/TownTrigger.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/TownTrigger.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E137E53-49C0-43EF-AC6B-459B3098691E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E1278D-D3EF-4536-8710-F136A58D48A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="5040" windowWidth="51320" windowHeight="15840" xr2:uid="{7ED654B3-1415-4137-840F-782E691C6D8F}"/>
   </bookViews>
@@ -757,7 +757,7 @@
         <v>2</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>31001</v>
       </c>
       <c r="F6">
         <v>8.4499999999999993</v>
